--- a/docs/Mapping_casi_uso/cittadinanza/Citt_023.xlsx
+++ b/docs/Mapping_casi_uso/cittadinanza/Citt_023.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="166">
   <si>
     <t>Sezione</t>
   </si>
@@ -294,6 +294,12 @@
   </si>
   <si>
     <t>flagFirmatario</t>
+  </si>
+  <si>
+    <t>Residenza al momento dell'evento originario</t>
+  </si>
+  <si>
+    <t>residenzaOriginaria</t>
   </si>
   <si>
     <t>Ulteriore cittadinanza di cui è in possesso</t>
@@ -562,11 +568,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H125"/>
+  <dimension ref="A1:H126"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="22.59765625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="38.875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="40.984375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.5625" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="45.0546875" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="30.5234375" customWidth="true" bestFit="true"/>
@@ -1502,10 +1508,10 @@
         <v>94</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>95</v>
@@ -1522,7 +1528,7 @@
         <v>31</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>9</v>
@@ -1531,7 +1537,7 @@
         <v>27</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F42" s="2" t="s">
         <v>10</v>
@@ -1542,19 +1548,19 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>97</v>
+        <v>31</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D43" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>98</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>10</v>
@@ -1565,19 +1571,19 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>10</v>
@@ -1588,19 +1594,19 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F45" s="2" t="s">
         <v>10</v>
@@ -1611,19 +1617,19 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>10</v>
@@ -1634,19 +1640,19 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>10</v>
@@ -1657,19 +1663,19 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>99</v>
+        <v>44</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>10</v>
@@ -1680,19 +1686,19 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B49" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C49" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>98</v>
-      </c>
       <c r="E49" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>10</v>
@@ -1703,19 +1709,19 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>10</v>
@@ -1726,19 +1732,19 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>10</v>
@@ -1749,19 +1755,19 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>10</v>
@@ -1772,19 +1778,19 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>10</v>
@@ -1795,19 +1801,19 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>10</v>
@@ -1818,19 +1824,19 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>10</v>
@@ -1841,19 +1847,19 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>105</v>
+        <v>60</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>10</v>
@@ -1864,19 +1870,19 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>107</v>
+        <v>63</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>10</v>
@@ -1887,19 +1893,19 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>64</v>
+        <v>108</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>65</v>
+        <v>109</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>10</v>
@@ -1910,19 +1916,19 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>108</v>
+        <v>64</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>10</v>
@@ -1933,19 +1939,19 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>10</v>
@@ -1956,19 +1962,19 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>10</v>
@@ -1979,19 +1985,19 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>10</v>
@@ -2002,19 +2008,19 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>10</v>
@@ -2025,19 +2031,19 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>10</v>
@@ -2048,19 +2054,19 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>10</v>
@@ -2071,19 +2077,19 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>10</v>
@@ -2094,19 +2100,19 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>10</v>
@@ -2117,19 +2123,19 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>10</v>
@@ -2140,19 +2146,19 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>10</v>
@@ -2163,19 +2169,19 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>10</v>
@@ -2186,19 +2192,19 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>10</v>
@@ -2209,19 +2215,19 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>10</v>
@@ -2232,19 +2238,19 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>116</v>
+        <v>87</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>10</v>
@@ -2255,7 +2261,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>117</v>
@@ -2264,10 +2270,10 @@
         <v>33</v>
       </c>
       <c r="D74" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E74" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>119</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>10</v>
@@ -2278,19 +2284,19 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D75" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B75" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D75" s="2" t="s">
+      <c r="E75" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>35</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>10</v>
@@ -2301,19 +2307,19 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>10</v>
@@ -2324,19 +2330,19 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>10</v>
@@ -2347,19 +2353,19 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>10</v>
@@ -2370,19 +2376,19 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>10</v>
@@ -2393,19 +2399,19 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>99</v>
+        <v>44</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>10</v>
@@ -2416,19 +2422,19 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>10</v>
@@ -2439,19 +2445,19 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>10</v>
@@ -2462,19 +2468,19 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>10</v>
@@ -2485,19 +2491,19 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>10</v>
@@ -2508,19 +2514,19 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>10</v>
@@ -2531,19 +2537,19 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>10</v>
@@ -2554,19 +2560,19 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>10</v>
@@ -2577,19 +2583,19 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>105</v>
+        <v>60</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>10</v>
@@ -2600,19 +2606,19 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>107</v>
+        <v>63</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>10</v>
@@ -2623,19 +2629,19 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>64</v>
+        <v>108</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>65</v>
+        <v>109</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>10</v>
@@ -2646,19 +2652,19 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>108</v>
+        <v>64</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>10</v>
@@ -2669,19 +2675,19 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>10</v>
@@ -2692,19 +2698,19 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>10</v>
@@ -2715,19 +2721,19 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>10</v>
@@ -2738,19 +2744,19 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>10</v>
@@ -2761,19 +2767,19 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>10</v>
@@ -2784,19 +2790,19 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>10</v>
@@ -2807,19 +2813,19 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>10</v>
@@ -2830,19 +2836,19 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>10</v>
@@ -2853,19 +2859,19 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>10</v>
@@ -2876,19 +2882,19 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>10</v>
@@ -2899,19 +2905,19 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>10</v>
@@ -2922,19 +2928,19 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>10</v>
@@ -2945,19 +2951,19 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>10</v>
@@ -2968,19 +2974,19 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>116</v>
+        <v>87</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>10</v>
@@ -2991,7 +2997,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>117</v>
@@ -3000,10 +3006,10 @@
         <v>33</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>10</v>
@@ -3014,53 +3020,53 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B107" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D107" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C107" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D107" s="2" t="s">
-        <v>125</v>
-      </c>
       <c r="E107" s="2" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>127</v>
+        <v>18</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B108" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E108" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C108" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D108" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E108" s="2" t="s">
+      <c r="F108" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G108" s="2" t="s">
         <v>129</v>
-      </c>
-      <c r="F108" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G108" s="2" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>130</v>
@@ -3069,7 +3075,7 @@
         <v>33</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>131</v>
@@ -3078,12 +3084,12 @@
         <v>10</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>132</v>
@@ -3092,7 +3098,7 @@
         <v>33</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>133</v>
@@ -3101,12 +3107,12 @@
         <v>10</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>134</v>
@@ -3115,7 +3121,7 @@
         <v>33</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>135</v>
@@ -3124,12 +3130,12 @@
         <v>10</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>136</v>
@@ -3138,44 +3144,44 @@
         <v>33</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>17</v>
+        <v>137</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>138</v>
+        <v>17</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>139</v>
@@ -3184,44 +3190,44 @@
         <v>33</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>20</v>
+        <v>140</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>141</v>
+        <v>20</v>
       </c>
       <c r="F115" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>142</v>
@@ -3230,7 +3236,7 @@
         <v>33</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>143</v>
@@ -3239,12 +3245,12 @@
         <v>10</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>144</v>
@@ -3253,7 +3259,7 @@
         <v>33</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>145</v>
@@ -3262,12 +3268,12 @@
         <v>10</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>146</v>
@@ -3276,7 +3282,7 @@
         <v>33</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>147</v>
@@ -3285,44 +3291,44 @@
         <v>10</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B119" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="B119" s="2" t="s">
+      <c r="C119" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E119" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="C119" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D119" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="E119" s="2" t="s">
-        <v>151</v>
-      </c>
       <c r="F119" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>18</v>
+        <v>129</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B120" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D120" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="C120" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D120" s="2" t="s">
-        <v>150</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>153</v>
@@ -3336,7 +3342,7 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>154</v>
@@ -3345,7 +3351,7 @@
         <v>9</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>155</v>
@@ -3359,7 +3365,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>156</v>
@@ -3368,7 +3374,7 @@
         <v>9</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>157</v>
@@ -3382,16 +3388,16 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>158</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>159</v>
@@ -3405,16 +3411,16 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>160</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>161</v>
@@ -3428,16 +3434,16 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>162</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>163</v>
@@ -3446,6 +3452,29 @@
         <v>10</v>
       </c>
       <c r="G125" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F126" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G126" s="2" t="s">
         <v>18</v>
       </c>
     </row>
